--- a/apps/api/data/CarbonCo_Calcul_Carbone_v2.xlsx
+++ b/apps/api/data/CarbonCo_Calcul_Carbone_v2.xlsx
@@ -7707,7 +7707,7 @@
       <c r="D10" s="44" t="n"/>
       <c r="E10" s="45">
         <f>SUM(E5:E9)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="847">
@@ -7801,7 +7801,7 @@
       <c r="D16" s="46" t="n"/>
       <c r="E16" s="47">
         <f>SUM(E13:E15)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="847">
@@ -7824,8 +7824,9 @@
       <c r="B19" s="33" t="n"/>
       <c r="C19" s="33" t="n"/>
       <c r="D19" s="33" t="n"/>
-      <c r="E19" s="38" t="n">
-        <v>2150</v>
+      <c r="E19" s="38">
+        <f>E10+E16</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -7837,8 +7838,9 @@
       <c r="B20" s="798" t="n"/>
       <c r="C20" s="799" t="n"/>
       <c r="D20" s="800" t="n"/>
-      <c r="E20" s="1009" t="n">
-        <v>38</v>
+      <c r="E20" s="1009">
+        <f>IF(E19=0,0,ROUND(E16/E19*100,1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -11212,7 +11214,7 @@
       </c>
       <c r="C6" s="42">
         <f>Scope_1!I16</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D6" s="1009">
         <f>IF($C$47=0,0,C6/$C$47)</f>
@@ -11257,7 +11259,7 @@
       </c>
       <c r="C7" s="42">
         <f>Scope_1!I30</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D7" s="1009">
         <f>IF($C$47=0,0,C7/$C$47)</f>
@@ -11302,7 +11304,7 @@
       </c>
       <c r="C8" s="42">
         <f>Scope_1!I42</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D8" s="1009">
         <f>IF($C$47=0,0,C8/$C$47)</f>
@@ -11347,7 +11349,7 @@
       </c>
       <c r="C9" s="42">
         <f>Scope_1!I54</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D9" s="1009">
         <f>IF($C$47=0,0,C9/$C$47)</f>
@@ -11386,8 +11388,9 @@
           <t>TOTAL SCOPE 1</t>
         </is>
       </c>
-      <c r="C10" s="105" t="n">
-        <v>1336</v>
+      <c r="C10" s="105">
+        <f>SUM(C6:C9)</f>
+        <v>0</v>
       </c>
       <c r="D10" s="1011">
         <f>IF($C$47=0,0,C10/$C$47)</f>
@@ -11462,7 +11465,7 @@
       </c>
       <c r="C13" s="42">
         <f>Scope_2!H16</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D13" s="1009">
         <f>IF($C$47=0,0,C13/$C$47)</f>
@@ -11501,7 +11504,7 @@
       </c>
       <c r="C14" s="42">
         <f>Scope_2!H29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D14" s="92" t="n"/>
       <c r="E14" s="92" t="n">
@@ -11531,8 +11534,9 @@
           <t>TOTAL SCOPE 2 (Location-based)</t>
         </is>
       </c>
-      <c r="C15" s="45" t="n">
-        <v>934</v>
+      <c r="C15" s="45">
+        <f>C13+C14</f>
+        <v>0</v>
       </c>
       <c r="D15" s="96" t="n"/>
       <c r="E15" s="96" t="n"/>
@@ -11560,7 +11564,7 @@
       </c>
       <c r="C16" s="42">
         <f>Scope_2!K16</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D16" s="92" t="n"/>
       <c r="E16" s="92" t="n"/>
@@ -11582,8 +11586,9 @@
           <t>TOTAL SCOPE 2 (Market-based)</t>
         </is>
       </c>
-      <c r="C17" s="36" t="n">
-        <v>1020</v>
+      <c r="C17" s="36">
+        <f>C16+C14</f>
+        <v>0</v>
       </c>
       <c r="D17" s="868" t="n"/>
       <c r="E17" s="868" t="n"/>
@@ -11649,7 +11654,7 @@
       </c>
       <c r="C20" s="42">
         <f>Scope_3!I19</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D20" s="1009">
         <f>IF($C$47=0,0,C20/$C$47)</f>
@@ -11694,7 +11699,7 @@
       </c>
       <c r="C21" s="42">
         <f>Scope_3!I30</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D21" s="1009">
         <f>IF($C$47=0,0,C21/$C$47)</f>
@@ -11739,7 +11744,7 @@
       </c>
       <c r="C22" s="42">
         <f>Scope_3!I38</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D22" s="1009">
         <f>IF($C$47=0,0,C22/$C$47)</f>
@@ -11784,7 +11789,7 @@
       </c>
       <c r="C23" s="42">
         <f>Scope_3!I51</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D23" s="1009">
         <f>IF($C$47=0,0,C23/$C$47)</f>
@@ -11829,7 +11834,7 @@
       </c>
       <c r="C24" s="42">
         <f>Scope_3!I57</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D24" s="1009">
         <f>IF($C$47=0,0,C24/$C$47)</f>
@@ -11874,7 +11879,7 @@
       </c>
       <c r="C25" s="42">
         <f>Scope_3!I63</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D25" s="1009">
         <f>IF($C$47=0,0,C25/$C$47)</f>
@@ -11919,7 +11924,7 @@
       </c>
       <c r="C26" s="42">
         <f>Scope_3!I69</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D26" s="1009">
         <f>IF($C$47=0,0,C26/$C$47)</f>
@@ -11964,7 +11969,7 @@
       </c>
       <c r="C27" s="42">
         <f>Scope_3!I77</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D27" s="1009">
         <f>IF($C$47=0,0,C27/$C$47)</f>
@@ -12009,7 +12014,7 @@
       </c>
       <c r="C28" s="42">
         <f>Scope_3!I87</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D28" s="1009">
         <f>IF($C$47=0,0,C28/$C$47)</f>
@@ -12054,7 +12059,7 @@
       </c>
       <c r="C29" s="42">
         <f>Scope_3!I95</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D29" s="1009">
         <f>IF($C$47=0,0,C29/$C$47)</f>
@@ -12099,7 +12104,7 @@
       </c>
       <c r="C30" s="42">
         <f>Scope_3!I105</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D30" s="1009">
         <f>IF($C$47=0,0,C30/$C$47)</f>
@@ -12144,7 +12149,7 @@
       </c>
       <c r="C31" s="42">
         <f>Scope_3!I113</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D31" s="1009">
         <f>IF($C$47=0,0,C31/$C$47)</f>
@@ -12189,7 +12194,7 @@
       </c>
       <c r="C32" s="42">
         <f>Scope_3!I121</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D32" s="1009">
         <f>IF($C$47=0,0,C32/$C$47)</f>
@@ -12234,7 +12239,7 @@
       </c>
       <c r="C33" s="42">
         <f>Scope_3!I129</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D33" s="1009">
         <f>IF($C$47=0,0,C33/$C$47)</f>
@@ -12279,7 +12284,7 @@
       </c>
       <c r="C34" s="42">
         <f>Scope_3!I137</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D34" s="1009">
         <f>IF($C$47=0,0,C34/$C$47)</f>
@@ -12318,8 +12323,9 @@
           <t>TOTAL SCOPE 3</t>
         </is>
       </c>
-      <c r="C35" s="107" t="n">
-        <v>3685</v>
+      <c r="C35" s="107">
+        <f>SUM(C20:C34)</f>
+        <v>0</v>
       </c>
       <c r="D35" s="98" t="n"/>
       <c r="E35" s="98" t="n"/>
@@ -12360,7 +12366,7 @@
       </c>
       <c r="C37" s="108">
         <f>C10+C15</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D37" s="100" t="n"/>
       <c r="E37" s="100" t="n"/>
@@ -12535,8 +12541,9 @@
           <t>TOTAL SCOPE 1 + 2 + 3</t>
         </is>
       </c>
-      <c r="C47" s="32" t="n">
-        <v>5955</v>
+      <c r="C47" s="32">
+        <f>C10+C15+C35</f>
+        <v>0</v>
       </c>
       <c r="D47" s="102" t="n"/>
       <c r="E47" s="102" t="n"/>
@@ -12596,8 +12603,9 @@
           <t>Intensité / CA (tCO2e/M€)</t>
         </is>
       </c>
-      <c r="C50" s="50" t="n">
-        <v>322</v>
+      <c r="C50" s="50">
+        <f>IF(Paramètres!B9=0,0,C47/(Paramètres!B9/1000000))</f>
+        <v>0</v>
       </c>
       <c r="D50" s="868" t="n"/>
       <c r="E50" s="868" t="n"/>
@@ -12619,8 +12627,9 @@
           <t>Intensité / salarié (tCO2e/ETP)</t>
         </is>
       </c>
-      <c r="C51" s="50" t="n">
-        <v>41</v>
+      <c r="C51" s="50">
+        <f>IF(Paramètres!B11=0,0,C47/Paramètres!B11)</f>
+        <v>0</v>
       </c>
       <c r="D51" s="868" t="n"/>
       <c r="E51" s="868" t="n"/>
@@ -12644,7 +12653,7 @@
       </c>
       <c r="C52" s="50">
         <f>IF(Paramètres!B12=0,0,C47*1000/Paramètres!B12)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D52" s="868" t="n"/>
       <c r="E52" s="868" t="n"/>
@@ -12666,8 +12675,9 @@
           <t>Part Scope 1 (%)</t>
         </is>
       </c>
-      <c r="C53" s="995" t="n">
-        <v>22.4</v>
+      <c r="C53" s="995">
+        <f>IF(C47=0,0,ROUND(C10/C47*100,1))</f>
+        <v>0</v>
       </c>
       <c r="D53" s="868" t="n"/>
       <c r="E53" s="868" t="n"/>
@@ -12689,8 +12699,9 @@
           <t>Part Scope 2 (%)</t>
         </is>
       </c>
-      <c r="C54" s="995" t="n">
-        <v>15.7</v>
+      <c r="C54" s="995">
+        <f>IF(C47=0,0,ROUND(C15/C47*100,1))</f>
+        <v>0</v>
       </c>
       <c r="D54" s="868" t="n"/>
       <c r="E54" s="868" t="n"/>
@@ -12712,8 +12723,9 @@
           <t>Part Scope 3 (%)</t>
         </is>
       </c>
-      <c r="C55" s="995" t="n">
-        <v>61.9</v>
+      <c r="C55" s="995">
+        <f>IF(C47=0,0,ROUND(C35/C47*100,1))</f>
+        <v>0</v>
       </c>
       <c r="D55" s="868" t="n"/>
       <c r="E55" s="868" t="n"/>
@@ -13124,9 +13136,7 @@
           <t>Année de référence (baseline)</t>
         </is>
       </c>
-      <c r="B4" s="275" t="n">
-        <v>2019</v>
-      </c>
+      <c r="B4" s="275"/>
       <c r="C4" s="868" t="n"/>
       <c r="D4" s="868" t="n"/>
       <c r="E4" s="868" t="n"/>
@@ -13147,9 +13157,7 @@
           <t>Émissions Scope 1+2 baseline (tCO2e)</t>
         </is>
       </c>
-      <c r="B5" s="818" t="n">
-        <v>2800</v>
-      </c>
+      <c r="B5" s="818"/>
       <c r="C5" s="868" t="n"/>
       <c r="D5" s="868" t="n"/>
       <c r="E5" s="868" t="n"/>
@@ -13170,9 +13178,7 @@
           <t>Émissions Scope 3 baseline (tCO2e)</t>
         </is>
       </c>
-      <c r="B6" s="818" t="n">
-        <v>4200</v>
-      </c>
+      <c r="B6" s="818"/>
       <c r="C6" s="868" t="n"/>
       <c r="D6" s="868" t="n"/>
       <c r="E6" s="868" t="n"/>
@@ -13215,7 +13221,7 @@
     <row r="8">
       <c r="A8" s="821" t="inlineStr">
         <is>
-          <t>Taux réduction annuel S1+2 (%)</t>
+          <t>Réduction visée Scope 1+2 à l'horizon (%)</t>
         </is>
       </c>
       <c r="B8" s="819" t="n">
@@ -13238,7 +13244,7 @@
     <row r="9">
       <c r="A9" s="821" t="inlineStr">
         <is>
-          <t>Taux réduction annuel Scope 3 (%)</t>
+          <t>Réduction visée Scope 3 à l'horizon (%)</t>
         </is>
       </c>
       <c r="B9" s="275" t="n">
@@ -14346,7 +14352,7 @@
     <row r="4" ht="15.75" customHeight="1" s="847" thickBot="1">
       <c r="A4" s="823" t="inlineStr">
         <is>
-          <t>Prix quota EU ETS (€/tCO2)</t>
+          <t>Prix du quota EU ETS (€/tCO2) — à actualiser</t>
         </is>
       </c>
       <c r="B4" s="825" t="n">
@@ -14356,13 +14362,22 @@
     <row r="5" ht="15.75" customHeight="1" s="847" thickBot="1">
       <c r="A5" s="824" t="inlineStr">
         <is>
-          <t>Trimestre de déclaration</t>
-        </is>
-      </c>
-      <c r="B5" s="826" t="inlineStr">
-        <is>
-          <t>T1 2026</t>
-        </is>
+          <t>Année des importations (déclaration annuelle)</t>
+        </is>
+      </c>
+      <c r="B5" s="826" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Part des émissions couverte par des certificats (règl. (UE) 2023/956, art. 31)</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>IF(B5="","",IF(B5&lt;2026,0,IF(B5=2026,0.025,IF(B5=2027,0.05,IF(B5=2028,0.1,IF(B5=2029,0.225,IF(B5=2030,0.485,IF(B5=2031,0.61,IF(B5=2032,0.735,IF(B5=2033,0.86,1))))))))))</f>
+        <v>0.025</v>
       </c>
     </row>
     <row r="8" ht="39.75" customHeight="1" s="847">
@@ -14455,7 +14470,7 @@
       </c>
       <c r="I9" s="42">
         <f>IF(B9="",0,E9*F9+IF(G9="OUI",E9*H9,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>0</v>
@@ -14469,8 +14484,8 @@
         <v/>
       </c>
       <c r="M9" s="60">
-        <f>MAX(0,I9*$B$4-K9)</f>
-        <v/>
+        <f>IF(OR(B9="",$B$6=""),0,MAX(0,I9*$B$4*$B$6-K9))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -14496,7 +14511,7 @@
       </c>
       <c r="I10" s="42">
         <f>IF(B10="",0,E10*F10+IF(G10="OUI",E10*H10,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J10" s="15" t="n">
         <v>0</v>
@@ -14510,8 +14525,8 @@
         <v/>
       </c>
       <c r="M10" s="60">
-        <f>MAX(0,I10*$B$4-K10)</f>
-        <v/>
+        <f>IF(OR(B10="",$B$6=""),0,MAX(0,I10*$B$4*$B$6-K10))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -14537,7 +14552,7 @@
       </c>
       <c r="I11" s="42">
         <f>IF(B11="",0,E11*F11+IF(G11="OUI",E11*H11,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>0</v>
@@ -14551,8 +14566,8 @@
         <v/>
       </c>
       <c r="M11" s="60">
-        <f>MAX(0,I11*$B$4-K11)</f>
-        <v/>
+        <f>IF(OR(B11="",$B$6=""),0,MAX(0,I11*$B$4*$B$6-K11))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -14578,7 +14593,7 @@
       </c>
       <c r="I12" s="42">
         <f>IF(B12="",0,E12*F12+IF(G12="OUI",E12*H12,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J12" s="15" t="n">
         <v>0</v>
@@ -14592,8 +14607,8 @@
         <v/>
       </c>
       <c r="M12" s="60">
-        <f>MAX(0,I12*$B$4-K12)</f>
-        <v/>
+        <f>IF(OR(B12="",$B$6=""),0,MAX(0,I12*$B$4*$B$6-K12))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14619,7 +14634,7 @@
       </c>
       <c r="I13" s="42">
         <f>IF(B13="",0,E13*F13+IF(G13="OUI",E13*H13,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>0</v>
@@ -14633,8 +14648,8 @@
         <v/>
       </c>
       <c r="M13" s="60">
-        <f>MAX(0,I13*$B$4-K13)</f>
-        <v/>
+        <f>IF(OR(B13="",$B$6=""),0,MAX(0,I13*$B$4*$B$6-K13))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14660,7 +14675,7 @@
       </c>
       <c r="I14" s="42">
         <f>IF(B14="",0,E14*F14+IF(G14="OUI",E14*H14,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J14" s="15" t="n">
         <v>0</v>
@@ -14674,8 +14689,8 @@
         <v/>
       </c>
       <c r="M14" s="60">
-        <f>MAX(0,I14*$B$4-K14)</f>
-        <v/>
+        <f>IF(OR(B14="",$B$6=""),0,MAX(0,I14*$B$4*$B$6-K14))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14701,7 +14716,7 @@
       </c>
       <c r="I15" s="42">
         <f>IF(B15="",0,E15*F15+IF(G15="OUI",E15*H15,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J15" s="15" t="n">
         <v>0</v>
@@ -14715,8 +14730,8 @@
         <v/>
       </c>
       <c r="M15" s="60">
-        <f>MAX(0,I15*$B$4-K15)</f>
-        <v/>
+        <f>IF(OR(B15="",$B$6=""),0,MAX(0,I15*$B$4*$B$6-K15))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14742,7 +14757,7 @@
       </c>
       <c r="I16" s="42">
         <f>IF(B16="",0,E16*F16+IF(G16="OUI",E16*H16,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J16" s="15" t="n">
         <v>0</v>
@@ -14756,8 +14771,8 @@
         <v/>
       </c>
       <c r="M16" s="60">
-        <f>MAX(0,I16*$B$4-K16)</f>
-        <v/>
+        <f>IF(OR(B16="",$B$6=""),0,MAX(0,I16*$B$4*$B$6-K16))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14783,7 +14798,7 @@
       </c>
       <c r="I17" s="42">
         <f>IF(B17="",0,E17*F17+IF(G17="OUI",E17*H17,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J17" s="15" t="n">
         <v>0</v>
@@ -14797,8 +14812,8 @@
         <v/>
       </c>
       <c r="M17" s="60">
-        <f>MAX(0,I17*$B$4-K17)</f>
-        <v/>
+        <f>IF(OR(B17="",$B$6=""),0,MAX(0,I17*$B$4*$B$6-K17))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14824,7 +14839,7 @@
       </c>
       <c r="I18" s="42">
         <f>IF(B18="",0,E18*F18+IF(G18="OUI",E18*H18,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J18" s="15" t="n">
         <v>0</v>
@@ -14838,8 +14853,8 @@
         <v/>
       </c>
       <c r="M18" s="60">
-        <f>MAX(0,I18*$B$4-K18)</f>
-        <v/>
+        <f>IF(OR(B18="",$B$6=""),0,MAX(0,I18*$B$4*$B$6-K18))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14865,7 +14880,7 @@
       </c>
       <c r="I19" s="42">
         <f>IF(B19="",0,E19*F19+IF(G19="OUI",E19*H19,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J19" s="15" t="n">
         <v>0</v>
@@ -14879,8 +14894,8 @@
         <v/>
       </c>
       <c r="M19" s="60">
-        <f>MAX(0,I19*$B$4-K19)</f>
-        <v/>
+        <f>IF(OR(B19="",$B$6=""),0,MAX(0,I19*$B$4*$B$6-K19))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14906,7 +14921,7 @@
       </c>
       <c r="I20" s="42">
         <f>IF(B20="",0,E20*F20+IF(G20="OUI",E20*H20,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J20" s="15" t="n">
         <v>0</v>
@@ -14920,8 +14935,8 @@
         <v/>
       </c>
       <c r="M20" s="60">
-        <f>MAX(0,I20*$B$4-K20)</f>
-        <v/>
+        <f>IF(OR(B20="",$B$6=""),0,MAX(0,I20*$B$4*$B$6-K20))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -14947,7 +14962,7 @@
       </c>
       <c r="I21" s="42">
         <f>IF(B21="",0,E21*F21+IF(G21="OUI",E21*H21,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J21" s="15" t="n">
         <v>0</v>
@@ -14961,8 +14976,8 @@
         <v/>
       </c>
       <c r="M21" s="60">
-        <f>MAX(0,I21*$B$4-K21)</f>
-        <v/>
+        <f>IF(OR(B21="",$B$6=""),0,MAX(0,I21*$B$4*$B$6-K21))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -14988,7 +15003,7 @@
       </c>
       <c r="I22" s="42">
         <f>IF(B22="",0,E22*F22+IF(G22="OUI",E22*H22,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J22" s="15" t="n">
         <v>0</v>
@@ -15002,8 +15017,8 @@
         <v/>
       </c>
       <c r="M22" s="60">
-        <f>MAX(0,I22*$B$4-K22)</f>
-        <v/>
+        <f>IF(OR(B22="",$B$6=""),0,MAX(0,I22*$B$4*$B$6-K22))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -15029,7 +15044,7 @@
       </c>
       <c r="I23" s="42">
         <f>IF(B23="",0,E23*F23+IF(G23="OUI",E23*H23,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>0</v>
@@ -15043,8 +15058,8 @@
         <v/>
       </c>
       <c r="M23" s="60">
-        <f>MAX(0,I23*$B$4-K23)</f>
-        <v/>
+        <f>IF(OR(B23="",$B$6=""),0,MAX(0,I23*$B$4*$B$6-K23))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -15076,8 +15091,9 @@
         <f>SUM(L9:L23)</f>
         <v/>
       </c>
-      <c r="M24" s="34" t="n">
-        <v>48000</v>
+      <c r="M24" s="34">
+        <f>SUM(M9:M23)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="847">
@@ -15346,7 +15362,7 @@
       <c r="E14" s="13" t="n"/>
       <c r="F14" s="13" t="n"/>
       <c r="G14" s="26">
-        <f>IF(AND(C14="O",E14="O",F14="O"),"O","N")</f>
+        <f>IF(AND(C14="O",D14&lt;&gt;"",E14="O",F14="O"),"O","N")</f>
         <v/>
       </c>
       <c r="H14" s="15" t="n">
@@ -15367,7 +15383,7 @@
       <c r="E15" s="13" t="n"/>
       <c r="F15" s="13" t="n"/>
       <c r="G15" s="26">
-        <f>IF(AND(C15="O",E15="O",F15="O"),"O","N")</f>
+        <f>IF(AND(C15="O",D15&lt;&gt;"",E15="O",F15="O"),"O","N")</f>
         <v/>
       </c>
       <c r="H15" s="15" t="n">
@@ -15388,7 +15404,7 @@
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
       <c r="G16" s="26">
-        <f>IF(AND(C16="O",E16="O",F16="O"),"O","N")</f>
+        <f>IF(AND(C16="O",D16&lt;&gt;"",E16="O",F16="O"),"O","N")</f>
         <v/>
       </c>
       <c r="H16" s="15" t="n">
@@ -15409,7 +15425,7 @@
       <c r="E17" s="13" t="n"/>
       <c r="F17" s="13" t="n"/>
       <c r="G17" s="26">
-        <f>IF(AND(C17="O",E17="O",F17="O"),"O","N")</f>
+        <f>IF(AND(C17="O",D17&lt;&gt;"",E17="O",F17="O"),"O","N")</f>
         <v/>
       </c>
       <c r="H17" s="15" t="n">
@@ -15430,7 +15446,7 @@
       <c r="E18" s="13" t="n"/>
       <c r="F18" s="13" t="n"/>
       <c r="G18" s="26">
-        <f>IF(AND(C18="O",E18="O",F18="O"),"O","N")</f>
+        <f>IF(AND(C18="O",D18&lt;&gt;"",E18="O",F18="O"),"O","N")</f>
         <v/>
       </c>
       <c r="H18" s="15" t="n">
@@ -15451,7 +15467,7 @@
       <c r="E19" s="13" t="n"/>
       <c r="F19" s="13" t="n"/>
       <c r="G19" s="26">
-        <f>IF(AND(C19="O",E19="O",F19="O"),"O","N")</f>
+        <f>IF(AND(C19="O",D19&lt;&gt;"",E19="O",F19="O"),"O","N")</f>
         <v/>
       </c>
       <c r="H19" s="15" t="n">
@@ -15472,7 +15488,7 @@
       <c r="E20" s="13" t="n"/>
       <c r="F20" s="13" t="n"/>
       <c r="G20" s="26">
-        <f>IF(AND(C20="O",E20="O",F20="O"),"O","N")</f>
+        <f>IF(AND(C20="O",D20&lt;&gt;"",E20="O",F20="O"),"O","N")</f>
         <v/>
       </c>
       <c r="H20" s="15" t="n">
@@ -15493,7 +15509,7 @@
       <c r="E21" s="13" t="n"/>
       <c r="F21" s="13" t="n"/>
       <c r="G21" s="26">
-        <f>IF(AND(C21="O",E21="O",F21="O"),"O","N")</f>
+        <f>IF(AND(C21="O",D21&lt;&gt;"",E21="O",F21="O"),"O","N")</f>
         <v/>
       </c>
       <c r="H21" s="15" t="n">
@@ -15514,7 +15530,7 @@
       <c r="E22" s="13" t="n"/>
       <c r="F22" s="13" t="n"/>
       <c r="G22" s="26">
-        <f>IF(AND(C22="O",E22="O",F22="O"),"O","N")</f>
+        <f>IF(AND(C22="O",D22&lt;&gt;"",E22="O",F22="O"),"O","N")</f>
         <v/>
       </c>
       <c r="H22" s="15" t="n">
@@ -15535,7 +15551,7 @@
       <c r="E23" s="13" t="n"/>
       <c r="F23" s="13" t="n"/>
       <c r="G23" s="26">
-        <f>IF(AND(C23="O",E23="O",F23="O"),"O","N")</f>
+        <f>IF(AND(C23="O",D23&lt;&gt;"",E23="O",F23="O"),"O","N")</f>
         <v/>
       </c>
       <c r="H23" s="15" t="n">
@@ -15610,8 +15626,9 @@
         <f>SUMPRODUCT((G14:G23="O")*(H14:H23))</f>
         <v/>
       </c>
-      <c r="E27" s="1009" t="n">
-        <v>35</v>
+      <c r="E27" s="1009">
+        <f>IF(F27=0,0,ROUND(D27/F27*100,1))</f>
+        <v>0</v>
       </c>
       <c r="F27" s="60">
         <f>Paramètres!B9</f>
@@ -15636,8 +15653,9 @@
         <f>SUMPRODUCT((G14:G23="O")*(I14:I23))</f>
         <v/>
       </c>
-      <c r="E28" s="1009" t="n">
-        <v>28</v>
+      <c r="E28" s="1009">
+        <f>IF(F28=0,0,ROUND(D28/F28*100,1))</f>
+        <v>0</v>
       </c>
       <c r="F28" s="60">
         <f>Paramètres!B14</f>
@@ -15662,8 +15680,9 @@
         <f>SUMPRODUCT((G14:G23="O")*(J14:J23))</f>
         <v/>
       </c>
-      <c r="E29" s="1009" t="n">
-        <v>22</v>
+      <c r="E29" s="1009">
+        <f>IF(F29=0,0,ROUND(D29/F29*100,1))</f>
+        <v>0</v>
       </c>
       <c r="F29" s="60">
         <f>Paramètres!B15</f>
@@ -54955,11 +54974,7 @@
           <t>Raison sociale</t>
         </is>
       </c>
-      <c r="B4" s="833" t="inlineStr">
-        <is>
-          <t>Acme Industries SAS</t>
-        </is>
-      </c>
+      <c r="B4" s="833"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="847" thickBot="1">
       <c r="A5" s="793" t="inlineStr">
@@ -54975,16 +54990,8 @@
           <t>Secteur d'activité</t>
         </is>
       </c>
-      <c r="B6" s="834" t="inlineStr">
-        <is>
-          <t>Fabrication métallique</t>
-        </is>
-      </c>
-      <c r="C6" s="838" t="inlineStr">
-        <is>
-          <t>25.11</t>
-        </is>
-      </c>
+      <c r="B6" s="834"/>
+      <c r="C6" s="838"/>
       <c r="D6" s="839" t="n"/>
     </row>
     <row r="7">
@@ -54993,9 +55000,7 @@
           <t>Année de reporting</t>
         </is>
       </c>
-      <c r="B7" s="835" t="n">
-        <v>2024</v>
-      </c>
+      <c r="B7" s="835"/>
     </row>
     <row r="8">
       <c r="A8" s="793" t="inlineStr">
@@ -55003,11 +55008,7 @@
           <t>Période</t>
         </is>
       </c>
-      <c r="B8" s="834" t="inlineStr">
-        <is>
-          <t>01/01/2025 — 31/12/2025</t>
-        </is>
-      </c>
+      <c r="B8" s="834"/>
     </row>
     <row r="9">
       <c r="A9" s="793" t="inlineStr">
@@ -55015,9 +55016,7 @@
           <t>Chiffre d'affaires net (€)</t>
         </is>
       </c>
-      <c r="B9" s="836" t="n">
-        <v>18500000</v>
-      </c>
+      <c r="B9" s="836"/>
     </row>
     <row r="10">
       <c r="A10" s="793" t="inlineStr">
@@ -55025,9 +55024,7 @@
           <t>Total du bilan (€)</t>
         </is>
       </c>
-      <c r="B10" s="836" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" s="836"/>
     </row>
     <row r="11">
       <c r="A11" s="793" t="inlineStr">
@@ -55035,9 +55032,7 @@
           <t>Effectifs (ETP)</t>
         </is>
       </c>
-      <c r="B11" s="835" t="n">
-        <v>145</v>
-      </c>
+      <c r="B11" s="835"/>
     </row>
     <row r="12">
       <c r="A12" s="793" t="inlineStr">
@@ -55045,9 +55040,7 @@
           <t>Surface occupée (m²)</t>
         </is>
       </c>
-      <c r="B12" s="835" t="n">
-        <v>4200</v>
-      </c>
+      <c r="B12" s="835"/>
     </row>
     <row r="13">
       <c r="A13" s="793" t="inlineStr">
@@ -55055,9 +55048,7 @@
           <t>Nombre de sites</t>
         </is>
       </c>
-      <c r="B13" s="835" t="n">
-        <v>0</v>
-      </c>
+      <c r="B13" s="835"/>
     </row>
     <row r="14">
       <c r="A14" s="793" t="inlineStr">
@@ -55065,9 +55056,7 @@
           <t>CapEx total entreprise (€)</t>
         </is>
       </c>
-      <c r="B14" s="836" t="n">
-        <v>2400000</v>
-      </c>
+      <c r="B14" s="836"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="847" thickBot="1">
       <c r="A15" s="794" t="inlineStr">
@@ -55075,9 +55064,7 @@
           <t>OpEx éligible Taxonomie (€)</t>
         </is>
       </c>
-      <c r="B15" s="837" t="n">
-        <v>620000</v>
-      </c>
+      <c r="B15" s="837"/>
       <c r="C15" s="16" t="inlineStr">
         <is>
           <t>(R&amp;D + rénovation bâtiments + leases CT + maintenance)</t>
